--- a/游戏机制/生物生成/群系和结构的生成生物列表/biome.xlsx
+++ b/游戏机制/生物生成/群系和结构的生成生物列表/biome.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="193">
   <si>
     <t>群系</t>
   </si>
@@ -119,6 +119,9 @@
     <t>crimson_forest</t>
   </si>
   <si>
+    <t>dappled_forest</t>
+  </si>
+  <si>
     <t>dark_forest</t>
   </si>
   <si>
@@ -416,6 +419,9 @@
     <t>rabbit</t>
   </si>
   <si>
+    <t>fox</t>
+  </si>
+  <si>
     <t>polar_bear</t>
   </si>
   <si>
@@ -428,9 +434,6 @@
     <t>goat</t>
   </si>
   <si>
-    <t>fox</t>
-  </si>
-  <si>
     <t>frog</t>
   </si>
   <si>
@@ -482,6 +485,9 @@
     <t xml:space="preserve">  2 2-6</t>
   </si>
   <si>
+    <t xml:space="preserve">  4 2-4</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 12 2-3</t>
   </si>
   <si>
@@ -491,22 +497,19 @@
     <t xml:space="preserve">  8 2-3</t>
   </si>
   <si>
+    <t xml:space="preserve">  8 2-4</t>
+  </si>
+  <si>
     <t xml:space="preserve">  5 4</t>
   </si>
   <si>
     <t xml:space="preserve">  8 4-8</t>
   </si>
   <si>
-    <t xml:space="preserve">  8 2-4</t>
-  </si>
-  <si>
     <t xml:space="preserve">  2 4-8</t>
   </si>
   <si>
     <t xml:space="preserve">  5 1-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4 2-4</t>
   </si>
   <si>
     <t xml:space="preserve"> 10 2-5</t>
@@ -928,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1018,28 +1021,28 @@
         <v>515</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1050,31 +1053,31 @@
         <v>517</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -1085,10 +1088,10 @@
         <v>140</v>
       </c>
       <c r="L4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -1099,28 +1102,28 @@
         <v>515</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1131,28 +1134,28 @@
         <v>515</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1163,28 +1166,28 @@
         <v>515</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1195,31 +1198,31 @@
         <v>520</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1230,13 +1233,13 @@
         <v>15</v>
       </c>
       <c r="O9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1247,28 +1250,28 @@
         <v>515</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1276,34 +1279,31 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
-      </c>
-      <c r="N11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1311,7 +1311,34 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>520</v>
+      </c>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J12" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1319,34 +1346,7 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>520</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" t="s">
-        <v>95</v>
-      </c>
-      <c r="N13" t="s">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1357,31 +1357,31 @@
         <v>520</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1392,31 +1392,31 @@
         <v>520</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -1424,10 +1424,10 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>92</v>
@@ -1436,25 +1436,22 @@
         <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
-      </c>
-      <c r="R16" t="s">
-        <v>117</v>
-      </c>
-      <c r="S16" t="s">
-        <v>98</v>
+        <v>96</v>
+      </c>
+      <c r="N16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -1462,34 +1459,37 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>610</v>
+        <v>515</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
-      </c>
-      <c r="N17" t="s">
-        <v>91</v>
+        <v>96</v>
+      </c>
+      <c r="R17" t="s">
+        <v>118</v>
+      </c>
+      <c r="S17" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -1497,10 +1497,34 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>610</v>
+      </c>
+      <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s">
+        <v>91</v>
       </c>
       <c r="I18" t="s">
         <v>104</v>
+      </c>
+      <c r="J18" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -1511,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -1522,7 +1546,7 @@
         <v>10</v>
       </c>
       <c r="I20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -1530,31 +1554,10 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>515</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>103</v>
-      </c>
-      <c r="J21" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -1565,28 +1568,28 @@
         <v>515</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -1597,28 +1600,28 @@
         <v>515</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -1626,34 +1629,31 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
-      </c>
-      <c r="N24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -1661,31 +1661,34 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="N25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -1693,33 +1696,30 @@
         <v>48</v>
       </c>
       <c r="B26">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J26" t="s">
-        <v>95</v>
-      </c>
-      <c r="N26" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1728,31 +1728,34 @@
         <v>49</v>
       </c>
       <c r="B27">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J27" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="N27" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -1763,31 +1766,28 @@
         <v>515</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>95</v>
-      </c>
-      <c r="T28" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -1798,28 +1798,31 @@
         <v>515</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J29" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="T29" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -1827,34 +1830,31 @@
         <v>52</v>
       </c>
       <c r="B30">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J30" t="s">
-        <v>95</v>
-      </c>
-      <c r="K30" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -1862,34 +1862,34 @@
         <v>53</v>
       </c>
       <c r="B31">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J31" t="s">
-        <v>95</v>
-      </c>
-      <c r="N31" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="K31" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -1897,31 +1897,34 @@
         <v>54</v>
       </c>
       <c r="B32">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="N32" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -1929,34 +1932,31 @@
         <v>55</v>
       </c>
       <c r="B33">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J33" t="s">
-        <v>95</v>
-      </c>
-      <c r="U33" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -1964,31 +1964,34 @@
         <v>56</v>
       </c>
       <c r="B34">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J34" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="U34" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -1996,7 +1999,31 @@
         <v>57</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>515</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -2004,22 +2031,7 @@
         <v>58</v>
       </c>
       <c r="B36">
-        <v>168</v>
-      </c>
-      <c r="I36" t="s">
-        <v>105</v>
-      </c>
-      <c r="L36" t="s">
-        <v>98</v>
-      </c>
-      <c r="M36" t="s">
-        <v>111</v>
-      </c>
-      <c r="O36" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -2027,34 +2039,22 @@
         <v>59</v>
       </c>
       <c r="B37">
-        <v>520</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" t="s">
-        <v>90</v>
-      </c>
-      <c r="G37" t="s">
-        <v>90</v>
-      </c>
-      <c r="H37" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s">
-        <v>103</v>
-      </c>
-      <c r="J37" t="s">
-        <v>95</v>
-      </c>
-      <c r="N37" t="s">
-        <v>95</v>
+        <v>106</v>
+      </c>
+      <c r="L37" t="s">
+        <v>99</v>
+      </c>
+      <c r="M37" t="s">
+        <v>112</v>
+      </c>
+      <c r="O37" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -2062,31 +2062,34 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="N38" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -2094,31 +2097,31 @@
         <v>61</v>
       </c>
       <c r="B39">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -2126,31 +2129,31 @@
         <v>62</v>
       </c>
       <c r="B40">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
         <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -2161,28 +2164,28 @@
         <v>515</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -2193,31 +2196,28 @@
         <v>515</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>95</v>
-      </c>
-      <c r="V42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -2225,34 +2225,34 @@
         <v>65</v>
       </c>
       <c r="B43">
-        <v>615</v>
+        <v>515</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J43" t="s">
-        <v>95</v>
-      </c>
-      <c r="N43" t="s">
-        <v>112</v>
+        <v>96</v>
+      </c>
+      <c r="V43" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -2260,34 +2260,34 @@
         <v>66</v>
       </c>
       <c r="B44">
-        <v>515</v>
+        <v>615</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J44" t="s">
-        <v>95</v>
-      </c>
-      <c r="V44" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="N44" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -2298,31 +2298,31 @@
         <v>515</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -2330,10 +2330,34 @@
         <v>68</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>515</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" t="s">
+        <v>96</v>
+      </c>
+      <c r="F46" t="s">
+        <v>91</v>
+      </c>
+      <c r="G46" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46" t="s">
+        <v>91</v>
       </c>
       <c r="I46" t="s">
         <v>104</v>
+      </c>
+      <c r="J46" t="s">
+        <v>96</v>
+      </c>
+      <c r="V46" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -2341,31 +2365,10 @@
         <v>69</v>
       </c>
       <c r="B47">
-        <v>515</v>
-      </c>
-      <c r="C47" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" t="s">
-        <v>91</v>
-      </c>
-      <c r="E47" t="s">
-        <v>95</v>
-      </c>
-      <c r="F47" t="s">
-        <v>90</v>
-      </c>
-      <c r="G47" t="s">
-        <v>90</v>
-      </c>
-      <c r="H47" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="I47" t="s">
-        <v>103</v>
-      </c>
-      <c r="J47" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -2376,34 +2379,28 @@
         <v>515</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F48" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J48" t="s">
-        <v>95</v>
-      </c>
-      <c r="T48" t="s">
-        <v>117</v>
-      </c>
-      <c r="V48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -2414,28 +2411,34 @@
         <v>515</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D49" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F49" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J49" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="T49" t="s">
+        <v>118</v>
+      </c>
+      <c r="V49" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -2446,28 +2449,28 @@
         <v>515</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -2475,16 +2478,31 @@
         <v>73</v>
       </c>
       <c r="B51">
-        <v>71</v>
+        <v>515</v>
+      </c>
+      <c r="C51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E51" t="s">
+        <v>96</v>
       </c>
       <c r="F51" t="s">
-        <v>101</v>
+        <v>91</v>
+      </c>
+      <c r="G51" t="s">
+        <v>91</v>
+      </c>
+      <c r="H51" t="s">
+        <v>91</v>
       </c>
       <c r="I51" t="s">
-        <v>105</v>
-      </c>
-      <c r="L51" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="J51" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -2492,31 +2510,16 @@
         <v>74</v>
       </c>
       <c r="B52">
-        <v>515</v>
-      </c>
-      <c r="C52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="F52" t="s">
-        <v>90</v>
-      </c>
-      <c r="G52" t="s">
-        <v>90</v>
-      </c>
-      <c r="H52" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I52" t="s">
-        <v>103</v>
-      </c>
-      <c r="J52" t="s">
-        <v>95</v>
+        <v>106</v>
+      </c>
+      <c r="L52" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -2527,28 +2530,28 @@
         <v>515</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -2559,28 +2562,28 @@
         <v>515</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E54" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J54" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:24">
@@ -2588,34 +2591,31 @@
         <v>77</v>
       </c>
       <c r="B55">
-        <v>311</v>
+        <v>515</v>
+      </c>
+      <c r="C55" t="s">
+        <v>91</v>
       </c>
       <c r="D55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E55" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F55" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J55" t="s">
         <v>96</v>
-      </c>
-      <c r="W55" t="s">
-        <v>119</v>
-      </c>
-      <c r="X55" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -2623,34 +2623,34 @@
         <v>78</v>
       </c>
       <c r="B56">
-        <v>515</v>
-      </c>
-      <c r="C56" t="s">
-        <v>90</v>
+        <v>311</v>
       </c>
       <c r="D56" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E56" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" t="s">
         <v>95</v>
       </c>
-      <c r="F56" t="s">
-        <v>90</v>
-      </c>
       <c r="G56" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I56" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J56" t="s">
-        <v>95</v>
-      </c>
-      <c r="V56" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="W56" t="s">
+        <v>120</v>
+      </c>
+      <c r="X56" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -2658,34 +2658,34 @@
         <v>79</v>
       </c>
       <c r="B57">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F57" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J57" t="s">
-        <v>95</v>
-      </c>
-      <c r="U57" t="s">
-        <v>118</v>
+        <v>96</v>
+      </c>
+      <c r="V57" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -2693,31 +2693,34 @@
         <v>80</v>
       </c>
       <c r="B58">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C58" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E58" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F58" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G58" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J58" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="U58" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -2725,10 +2728,31 @@
         <v>81</v>
       </c>
       <c r="B59">
-        <v>10</v>
+        <v>515</v>
+      </c>
+      <c r="C59" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" t="s">
+        <v>96</v>
+      </c>
+      <c r="F59" t="s">
+        <v>91</v>
+      </c>
+      <c r="G59" t="s">
+        <v>91</v>
+      </c>
+      <c r="H59" t="s">
+        <v>91</v>
       </c>
       <c r="I59" t="s">
         <v>104</v>
+      </c>
+      <c r="J59" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:24">
@@ -2736,7 +2760,10 @@
         <v>82</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="I60" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -2744,34 +2771,7 @@
         <v>83</v>
       </c>
       <c r="B61">
-        <v>520</v>
-      </c>
-      <c r="C61" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61" t="s">
-        <v>91</v>
-      </c>
-      <c r="E61" t="s">
-        <v>95</v>
-      </c>
-      <c r="F61" t="s">
-        <v>90</v>
-      </c>
-      <c r="G61" t="s">
-        <v>90</v>
-      </c>
-      <c r="H61" t="s">
-        <v>90</v>
-      </c>
-      <c r="I61" t="s">
-        <v>103</v>
-      </c>
-      <c r="J61" t="s">
-        <v>95</v>
-      </c>
-      <c r="N61" t="s">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:24">
@@ -2779,10 +2779,34 @@
         <v>84</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>520</v>
+      </c>
+      <c r="C62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" t="s">
+        <v>92</v>
+      </c>
+      <c r="E62" t="s">
+        <v>96</v>
+      </c>
+      <c r="F62" t="s">
+        <v>91</v>
+      </c>
+      <c r="G62" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" t="s">
+        <v>91</v>
       </c>
       <c r="I62" t="s">
-        <v>105</v>
+        <v>104</v>
+      </c>
+      <c r="J62" t="s">
+        <v>96</v>
+      </c>
+      <c r="N62" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:24">
@@ -2790,31 +2814,10 @@
         <v>85</v>
       </c>
       <c r="B63">
-        <v>515</v>
-      </c>
-      <c r="C63" t="s">
-        <v>90</v>
-      </c>
-      <c r="D63" t="s">
-        <v>91</v>
-      </c>
-      <c r="E63" t="s">
-        <v>95</v>
-      </c>
-      <c r="F63" t="s">
-        <v>90</v>
-      </c>
-      <c r="G63" t="s">
-        <v>90</v>
-      </c>
-      <c r="H63" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>103</v>
-      </c>
-      <c r="J63" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:24">
@@ -2825,28 +2828,28 @@
         <v>515</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -2857,28 +2860,28 @@
         <v>515</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J65" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -2889,31 +2892,28 @@
         <v>515</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J66" t="s">
-        <v>95</v>
-      </c>
-      <c r="V66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -2924,28 +2924,63 @@
         <v>515</v>
       </c>
       <c r="C67" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" t="s">
+        <v>94</v>
+      </c>
+      <c r="E67" t="s">
+        <v>96</v>
+      </c>
+      <c r="F67" t="s">
+        <v>91</v>
+      </c>
+      <c r="G67" t="s">
+        <v>91</v>
+      </c>
+      <c r="H67" t="s">
+        <v>91</v>
+      </c>
+      <c r="I67" t="s">
+        <v>104</v>
+      </c>
+      <c r="J67" t="s">
+        <v>96</v>
+      </c>
+      <c r="V67" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22">
+      <c r="A68" t="s">
         <v>90</v>
       </c>
-      <c r="D67" t="s">
-        <v>91</v>
-      </c>
-      <c r="E67" t="s">
-        <v>95</v>
-      </c>
-      <c r="F67" t="s">
-        <v>90</v>
-      </c>
-      <c r="G67" t="s">
-        <v>90</v>
-      </c>
-      <c r="H67" t="s">
-        <v>90</v>
-      </c>
-      <c r="I67" t="s">
-        <v>103</v>
-      </c>
-      <c r="J67" t="s">
-        <v>95</v>
+      <c r="B68">
+        <v>515</v>
+      </c>
+      <c r="C68" t="s">
+        <v>91</v>
+      </c>
+      <c r="D68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" t="s">
+        <v>96</v>
+      </c>
+      <c r="F68" t="s">
+        <v>91</v>
+      </c>
+      <c r="G68" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68" t="s">
+        <v>91</v>
+      </c>
+      <c r="I68" t="s">
+        <v>104</v>
+      </c>
+      <c r="J68" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2955,7 +2990,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2971,64 +3006,64 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="T1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="U1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="V1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -3039,19 +3074,19 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -3062,22 +3097,22 @@
         <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -3088,7 +3123,7 @@
         <v>60</v>
       </c>
       <c r="J4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3099,7 +3134,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3110,16 +3145,16 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3130,13 +3165,13 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3155,7 +3190,7 @@
         <v>60</v>
       </c>
       <c r="J9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3163,19 +3198,25 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F10" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="L10" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3183,7 +3224,19 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3199,10 +3252,7 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="M13" t="s">
-        <v>143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3210,7 +3260,10 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3226,13 +3279,7 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>13</v>
-      </c>
-      <c r="L16" t="s">
-        <v>153</v>
-      </c>
-      <c r="N16" t="s">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -3240,7 +3287,13 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="L17" t="s">
+        <v>155</v>
+      </c>
+      <c r="O17" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -3272,22 +3325,7 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>46</v>
-      </c>
-      <c r="C21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" t="s">
-        <v>145</v>
-      </c>
-      <c r="G21" t="s">
-        <v>146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -3295,22 +3333,22 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
-        <v>145</v>
-      </c>
-      <c r="L22" t="s">
-        <v>154</v>
+        <v>146</v>
+      </c>
+      <c r="G22" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -3318,21 +3356,21 @@
         <v>45</v>
       </c>
       <c r="B23">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s">
-        <v>145</v>
-      </c>
-      <c r="O23" t="s">
+        <v>146</v>
+      </c>
+      <c r="L23" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3341,10 +3379,22 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="M24" t="s">
-        <v>143</v>
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" t="s">
+        <v>146</v>
+      </c>
+      <c r="P24" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -3352,10 +3402,10 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="P25" t="s">
-        <v>160</v>
+        <v>1</v>
+      </c>
+      <c r="N25" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -3363,7 +3413,10 @@
         <v>48</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -3371,16 +3424,7 @@
         <v>49</v>
       </c>
       <c r="B27">
-        <v>13</v>
-      </c>
-      <c r="L27" t="s">
-        <v>155</v>
-      </c>
-      <c r="O27" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -3388,13 +3432,16 @@
         <v>50</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L28" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="M28" t="s">
-        <v>143</v>
+        <v>154</v>
+      </c>
+      <c r="P28" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -3402,10 +3449,13 @@
         <v>51</v>
       </c>
       <c r="B29">
-        <v>5</v>
-      </c>
-      <c r="P29" t="s">
-        <v>160</v>
+        <v>11</v>
+      </c>
+      <c r="L29" t="s">
+        <v>148</v>
+      </c>
+      <c r="N29" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -3413,25 +3463,10 @@
         <v>52</v>
       </c>
       <c r="B30">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>141</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" t="s">
-        <v>144</v>
-      </c>
-      <c r="F30" t="s">
-        <v>145</v>
-      </c>
-      <c r="H30" t="s">
-        <v>148</v>
-      </c>
-      <c r="I30" t="s">
-        <v>143</v>
+        <v>5</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -3439,7 +3474,25 @@
         <v>53</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" t="s">
+        <v>149</v>
+      </c>
+      <c r="I31" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -3455,10 +3508,7 @@
         <v>55</v>
       </c>
       <c r="B33">
-        <v>10</v>
-      </c>
-      <c r="R33" t="s">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3466,16 +3516,10 @@
         <v>56</v>
       </c>
       <c r="B34">
-        <v>5</v>
-      </c>
-      <c r="C34" t="s">
-        <v>142</v>
-      </c>
-      <c r="L34" t="s">
-        <v>152</v>
-      </c>
-      <c r="S34" t="s">
-        <v>143</v>
+        <v>10</v>
+      </c>
+      <c r="R34" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3483,10 +3527,16 @@
         <v>57</v>
       </c>
       <c r="B35">
-        <v>8</v>
-      </c>
-      <c r="T35" t="s">
-        <v>157</v>
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>143</v>
+      </c>
+      <c r="L35" t="s">
+        <v>153</v>
+      </c>
+      <c r="S35" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3494,10 +3544,10 @@
         <v>58</v>
       </c>
       <c r="B36">
-        <v>60</v>
-      </c>
-      <c r="J36" t="s">
-        <v>150</v>
+        <v>8</v>
+      </c>
+      <c r="T36" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3505,7 +3555,10 @@
         <v>59</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="J37" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3513,19 +3566,7 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>40</v>
-      </c>
-      <c r="C38" t="s">
-        <v>141</v>
-      </c>
-      <c r="D38" t="s">
-        <v>104</v>
-      </c>
-      <c r="E38" t="s">
-        <v>104</v>
-      </c>
-      <c r="F38" t="s">
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3533,28 +3574,19 @@
         <v>61</v>
       </c>
       <c r="B39">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F39" t="s">
-        <v>145</v>
-      </c>
-      <c r="L39" t="s">
-        <v>154</v>
-      </c>
-      <c r="O39" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3565,25 +3597,25 @@
         <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L40" t="s">
-        <v>154</v>
-      </c>
-      <c r="O40" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q40" t="s">
+        <v>156</v>
+      </c>
+      <c r="M40" t="s">
         <v>158</v>
+      </c>
+      <c r="P40" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3591,7 +3623,28 @@
         <v>63</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="C41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E41" t="s">
+        <v>105</v>
+      </c>
+      <c r="F41" t="s">
+        <v>146</v>
+      </c>
+      <c r="L41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M41" t="s">
+        <v>158</v>
+      </c>
+      <c r="P41" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3599,25 +3652,7 @@
         <v>64</v>
       </c>
       <c r="B42">
-        <v>46</v>
-      </c>
-      <c r="C42" t="s">
-        <v>141</v>
-      </c>
-      <c r="D42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E42" t="s">
-        <v>104</v>
-      </c>
-      <c r="F42" t="s">
-        <v>145</v>
-      </c>
-      <c r="S42" t="s">
-        <v>163</v>
-      </c>
-      <c r="U42" t="s">
-        <v>164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3625,7 +3660,25 @@
         <v>65</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="C43" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" t="s">
+        <v>105</v>
+      </c>
+      <c r="F43" t="s">
+        <v>146</v>
+      </c>
+      <c r="S43" t="s">
+        <v>164</v>
+      </c>
+      <c r="U43" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3633,28 +3686,7 @@
         <v>66</v>
       </c>
       <c r="B44">
-        <v>52</v>
-      </c>
-      <c r="C44" t="s">
-        <v>141</v>
-      </c>
-      <c r="D44" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" t="s">
-        <v>104</v>
-      </c>
-      <c r="F44" t="s">
-        <v>145</v>
-      </c>
-      <c r="G44" t="s">
-        <v>147</v>
-      </c>
-      <c r="S44" t="s">
-        <v>96</v>
-      </c>
-      <c r="U44" t="s">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3662,34 +3694,28 @@
         <v>67</v>
       </c>
       <c r="B45">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G45" t="s">
-        <v>147</v>
-      </c>
-      <c r="O45" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="S45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U45" t="s">
-        <v>165</v>
-      </c>
-      <c r="V45" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3697,7 +3723,34 @@
         <v>68</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="C46" t="s">
+        <v>142</v>
+      </c>
+      <c r="D46" t="s">
+        <v>105</v>
+      </c>
+      <c r="E46" t="s">
+        <v>105</v>
+      </c>
+      <c r="F46" t="s">
+        <v>146</v>
+      </c>
+      <c r="G46" t="s">
+        <v>148</v>
+      </c>
+      <c r="P46" t="s">
+        <v>160</v>
+      </c>
+      <c r="S46" t="s">
+        <v>97</v>
+      </c>
+      <c r="U46" t="s">
+        <v>166</v>
+      </c>
+      <c r="V46" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3713,13 +3766,7 @@
         <v>70</v>
       </c>
       <c r="B48">
-        <v>11</v>
-      </c>
-      <c r="L48" t="s">
-        <v>147</v>
-      </c>
-      <c r="M48" t="s">
-        <v>143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -3727,13 +3774,13 @@
         <v>71</v>
       </c>
       <c r="B49">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L49" t="s">
-        <v>154</v>
-      </c>
-      <c r="P49" t="s">
-        <v>160</v>
+        <v>148</v>
+      </c>
+      <c r="N49" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -3741,28 +3788,13 @@
         <v>72</v>
       </c>
       <c r="B50">
-        <v>60</v>
-      </c>
-      <c r="C50" t="s">
-        <v>141</v>
-      </c>
-      <c r="D50" t="s">
-        <v>104</v>
-      </c>
-      <c r="E50" t="s">
-        <v>104</v>
-      </c>
-      <c r="F50" t="s">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="L50" t="s">
-        <v>154</v>
-      </c>
-      <c r="O50" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="Q50" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -3772,8 +3804,26 @@
       <c r="B51">
         <v>60</v>
       </c>
-      <c r="J51" t="s">
-        <v>150</v>
+      <c r="C51" t="s">
+        <v>142</v>
+      </c>
+      <c r="D51" t="s">
+        <v>105</v>
+      </c>
+      <c r="E51" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" t="s">
+        <v>146</v>
+      </c>
+      <c r="L51" t="s">
+        <v>156</v>
+      </c>
+      <c r="M51" t="s">
+        <v>158</v>
+      </c>
+      <c r="P51" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -3781,22 +3831,10 @@
         <v>74</v>
       </c>
       <c r="B52">
-        <v>58</v>
-      </c>
-      <c r="C52" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" t="s">
-        <v>104</v>
-      </c>
-      <c r="E52" t="s">
-        <v>144</v>
-      </c>
-      <c r="F52" t="s">
-        <v>145</v>
-      </c>
-      <c r="O52" t="s">
-        <v>158</v>
+        <v>60</v>
+      </c>
+      <c r="J52" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -3804,7 +3842,22 @@
         <v>75</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" t="s">
+        <v>105</v>
+      </c>
+      <c r="E53" t="s">
+        <v>145</v>
+      </c>
+      <c r="F53" t="s">
+        <v>146</v>
+      </c>
+      <c r="P53" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -3828,25 +3881,7 @@
         <v>78</v>
       </c>
       <c r="B56">
-        <v>46</v>
-      </c>
-      <c r="C56" t="s">
-        <v>141</v>
-      </c>
-      <c r="D56" t="s">
-        <v>104</v>
-      </c>
-      <c r="E56" t="s">
-        <v>104</v>
-      </c>
-      <c r="F56" t="s">
-        <v>145</v>
-      </c>
-      <c r="S56" t="s">
-        <v>163</v>
-      </c>
-      <c r="U56" t="s">
-        <v>164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -3854,22 +3889,25 @@
         <v>79</v>
       </c>
       <c r="B57">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F57" t="s">
-        <v>145</v>
-      </c>
-      <c r="R57" t="s">
-        <v>162</v>
+        <v>146</v>
+      </c>
+      <c r="S57" t="s">
+        <v>164</v>
+      </c>
+      <c r="U57" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -3877,28 +3915,22 @@
         <v>80</v>
       </c>
       <c r="B58">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E58" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F58" t="s">
-        <v>145</v>
-      </c>
-      <c r="L58" t="s">
-        <v>154</v>
-      </c>
-      <c r="O58" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>158</v>
+        <v>146</v>
+      </c>
+      <c r="R58" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -3906,7 +3938,28 @@
         <v>81</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="C59" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" t="s">
+        <v>105</v>
+      </c>
+      <c r="F59" t="s">
+        <v>146</v>
+      </c>
+      <c r="L59" t="s">
+        <v>156</v>
+      </c>
+      <c r="M59" t="s">
+        <v>158</v>
+      </c>
+      <c r="P59" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -3930,10 +3983,7 @@
         <v>84</v>
       </c>
       <c r="B62">
-        <v>60</v>
-      </c>
-      <c r="J62" t="s">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -3941,22 +3991,10 @@
         <v>85</v>
       </c>
       <c r="B63">
-        <v>45</v>
-      </c>
-      <c r="C63" t="s">
-        <v>141</v>
-      </c>
-      <c r="D63" t="s">
-        <v>104</v>
-      </c>
-      <c r="E63" t="s">
-        <v>104</v>
-      </c>
-      <c r="F63" t="s">
-        <v>145</v>
-      </c>
-      <c r="V63" t="s">
-        <v>166</v>
+        <v>60</v>
+      </c>
+      <c r="J63" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -3967,19 +4005,19 @@
         <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="V64" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -3990,19 +4028,19 @@
         <v>45</v>
       </c>
       <c r="C65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="V65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -4010,28 +4048,22 @@
         <v>88</v>
       </c>
       <c r="B66">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F66" t="s">
-        <v>145</v>
-      </c>
-      <c r="G66" t="s">
-        <v>147</v>
-      </c>
-      <c r="S66" t="s">
-        <v>96</v>
-      </c>
-      <c r="U66" t="s">
-        <v>165</v>
+        <v>146</v>
+      </c>
+      <c r="V66" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -4039,25 +4071,54 @@
         <v>89</v>
       </c>
       <c r="B67">
+        <v>52</v>
+      </c>
+      <c r="C67" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" t="s">
+        <v>105</v>
+      </c>
+      <c r="E67" t="s">
+        <v>105</v>
+      </c>
+      <c r="F67" t="s">
+        <v>146</v>
+      </c>
+      <c r="G67" t="s">
+        <v>148</v>
+      </c>
+      <c r="S67" t="s">
+        <v>97</v>
+      </c>
+      <c r="U67" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
         <v>48</v>
       </c>
-      <c r="C67" t="s">
-        <v>141</v>
-      </c>
-      <c r="D67" t="s">
-        <v>104</v>
-      </c>
-      <c r="E67" t="s">
-        <v>104</v>
-      </c>
-      <c r="F67" t="s">
-        <v>145</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="C68" t="s">
+        <v>142</v>
+      </c>
+      <c r="D68" t="s">
+        <v>105</v>
+      </c>
+      <c r="E68" t="s">
+        <v>105</v>
+      </c>
+      <c r="F68" t="s">
         <v>146</v>
       </c>
-      <c r="O67" t="s">
-        <v>159</v>
+      <c r="G68" t="s">
+        <v>147</v>
+      </c>
+      <c r="P68" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -4067,7 +4128,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4083,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4094,7 +4155,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4105,7 +4166,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4124,7 +4185,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4135,7 +4196,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4146,7 +4207,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4157,7 +4218,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4176,7 +4237,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4187,7 +4248,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4195,7 +4256,10 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4203,10 +4267,7 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4217,7 +4278,7 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4228,7 +4289,7 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4239,7 +4300,7 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4250,7 +4311,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4258,7 +4319,10 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4282,10 +4346,7 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4296,7 +4357,7 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4307,7 +4368,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4318,7 +4379,7 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4329,7 +4390,7 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4340,7 +4401,7 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4351,7 +4412,7 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4362,7 +4423,7 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4373,7 +4434,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4384,7 +4445,7 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4395,7 +4456,7 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -4406,7 +4467,7 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -4417,7 +4478,7 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4428,7 +4489,7 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -4439,7 +4500,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -4447,7 +4508,10 @@
         <v>58</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4455,10 +4519,7 @@
         <v>59</v>
       </c>
       <c r="B37">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -4469,7 +4530,7 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4480,7 +4541,7 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -4491,7 +4552,7 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -4502,7 +4563,7 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -4513,7 +4574,7 @@
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -4524,7 +4585,7 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -4535,7 +4596,7 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -4546,7 +4607,7 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -4554,7 +4615,10 @@
         <v>68</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -4562,10 +4626,7 @@
         <v>69</v>
       </c>
       <c r="B47">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -4576,7 +4637,7 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -4587,7 +4648,7 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -4598,7 +4659,7 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -4606,7 +4667,10 @@
         <v>73</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -4614,10 +4678,7 @@
         <v>74</v>
       </c>
       <c r="B52">
-        <v>10</v>
-      </c>
-      <c r="C52" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -4628,7 +4689,7 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -4639,7 +4700,7 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -4650,7 +4711,7 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -4661,7 +4722,7 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -4672,7 +4733,7 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -4683,7 +4744,7 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -4691,7 +4752,10 @@
         <v>81</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -4707,10 +4771,7 @@
         <v>83</v>
       </c>
       <c r="B61">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -4718,7 +4779,10 @@
         <v>84</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -4726,10 +4790,7 @@
         <v>85</v>
       </c>
       <c r="B63">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -4740,7 +4801,7 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -4751,7 +4812,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -4762,7 +4823,7 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -4773,7 +4834,18 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -4783,7 +4855,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4799,16 +4871,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4867,10 +4939,10 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4894,13 +4966,7 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" t="s">
-        <v>176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4908,7 +4974,13 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4916,10 +4988,7 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4927,16 +4996,10 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>174</v>
-      </c>
-      <c r="E14" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" t="s">
-        <v>179</v>
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4944,10 +5007,16 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
         <v>175</v>
+      </c>
+      <c r="E15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4955,7 +5024,10 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5019,10 +5091,7 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>15</v>
-      </c>
-      <c r="D24" t="s">
-        <v>176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5030,7 +5099,10 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -5038,10 +5110,7 @@
         <v>48</v>
       </c>
       <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -5049,7 +5118,10 @@
         <v>49</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -5081,16 +5153,7 @@
         <v>53</v>
       </c>
       <c r="B31">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>173</v>
-      </c>
-      <c r="E31" t="s">
-        <v>160</v>
-      </c>
-      <c r="F31" t="s">
-        <v>179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -5098,10 +5161,16 @@
         <v>54</v>
       </c>
       <c r="B32">
-        <v>25</v>
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32" t="s">
+        <v>162</v>
       </c>
       <c r="F32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -5112,7 +5181,7 @@
         <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -5120,7 +5189,10 @@
         <v>56</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="F34" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -5144,10 +5216,7 @@
         <v>59</v>
       </c>
       <c r="B37">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -5155,7 +5224,10 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -5195,10 +5267,7 @@
         <v>65</v>
       </c>
       <c r="B43">
-        <v>5</v>
-      </c>
-      <c r="D43" t="s">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -5206,7 +5275,10 @@
         <v>66</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -5342,13 +5414,7 @@
         <v>83</v>
       </c>
       <c r="B61">
-        <v>40</v>
-      </c>
-      <c r="E61" t="s">
-        <v>178</v>
-      </c>
-      <c r="F61" t="s">
-        <v>179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5356,7 +5422,13 @@
         <v>84</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="E62" t="s">
+        <v>179</v>
+      </c>
+      <c r="F62" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5396,6 +5468,14 @@
         <v>89</v>
       </c>
       <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
         <v>0</v>
       </c>
     </row>
@@ -5406,7 +5486,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5422,13 +5502,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5487,10 +5567,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5514,13 +5594,7 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D11" t="s">
-        <v>107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5528,7 +5602,13 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5536,13 +5616,7 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" t="s">
-        <v>107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5550,16 +5624,13 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>185</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5567,16 +5638,16 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5584,7 +5655,16 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5648,13 +5728,7 @@
         <v>46</v>
       </c>
       <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5662,7 +5736,13 @@
         <v>47</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5670,10 +5750,7 @@
         <v>48</v>
       </c>
       <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5681,7 +5758,10 @@
         <v>49</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5713,16 +5793,7 @@
         <v>53</v>
       </c>
       <c r="B31">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" t="s">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5730,7 +5801,16 @@
         <v>54</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>188</v>
+      </c>
+      <c r="D32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5770,16 +5850,7 @@
         <v>59</v>
       </c>
       <c r="B37">
-        <v>7</v>
-      </c>
-      <c r="C37" t="s">
-        <v>184</v>
-      </c>
-      <c r="D37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E37" t="s">
-        <v>143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -5787,7 +5858,16 @@
         <v>60</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5827,10 +5907,7 @@
         <v>65</v>
       </c>
       <c r="B43">
-        <v>2</v>
-      </c>
-      <c r="C43" t="s">
-        <v>186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -5838,7 +5915,10 @@
         <v>66</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -5974,16 +6054,7 @@
         <v>83</v>
       </c>
       <c r="B61">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s">
-        <v>104</v>
-      </c>
-      <c r="D61" t="s">
-        <v>95</v>
-      </c>
-      <c r="E61" t="s">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -5991,7 +6062,16 @@
         <v>84</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>105</v>
+      </c>
+      <c r="D62" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -6031,6 +6111,14 @@
         <v>89</v>
       </c>
       <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
         <v>0</v>
       </c>
     </row>
@@ -6041,7 +6129,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6057,7 +6145,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6068,7 +6156,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6079,7 +6167,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6098,7 +6186,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6109,7 +6197,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6120,7 +6208,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6131,7 +6219,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6150,7 +6238,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6161,7 +6249,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6169,7 +6257,10 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6177,10 +6268,7 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6191,7 +6279,7 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6202,7 +6290,7 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6213,7 +6301,7 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6224,7 +6312,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6232,7 +6320,10 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6256,10 +6347,7 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6270,7 +6358,7 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6281,7 +6369,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6292,7 +6380,7 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6303,7 +6391,7 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6314,7 +6402,7 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6325,7 +6413,7 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6336,7 +6424,7 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6347,7 +6435,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6358,7 +6446,7 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6369,7 +6457,7 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6380,7 +6468,7 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6391,7 +6479,7 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6402,7 +6490,7 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6413,7 +6501,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6421,7 +6509,10 @@
         <v>58</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6429,10 +6520,7 @@
         <v>59</v>
       </c>
       <c r="B37">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6443,7 +6531,7 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6454,7 +6542,7 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6465,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6476,7 +6564,7 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6487,7 +6575,7 @@
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6498,7 +6586,7 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6509,7 +6597,7 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6520,7 +6608,7 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6528,7 +6616,10 @@
         <v>68</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6536,10 +6627,7 @@
         <v>69</v>
       </c>
       <c r="B47">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6550,7 +6638,7 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6561,7 +6649,7 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6572,7 +6660,7 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6580,7 +6668,10 @@
         <v>73</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6588,10 +6679,7 @@
         <v>74</v>
       </c>
       <c r="B52">
-        <v>10</v>
-      </c>
-      <c r="C52" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6602,7 +6690,7 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6613,7 +6701,7 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6621,7 +6709,10 @@
         <v>77</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6629,10 +6720,7 @@
         <v>78</v>
       </c>
       <c r="B56">
-        <v>10</v>
-      </c>
-      <c r="C56" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6643,7 +6731,7 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6654,7 +6742,7 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6662,7 +6750,10 @@
         <v>81</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6678,10 +6769,7 @@
         <v>83</v>
       </c>
       <c r="B61">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -6689,7 +6777,10 @@
         <v>84</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -6697,10 +6788,7 @@
         <v>85</v>
       </c>
       <c r="B63">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -6711,7 +6799,7 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -6722,7 +6810,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -6733,7 +6821,7 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -6744,7 +6832,18 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -6754,7 +6853,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6770,7 +6869,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6893,7 +6992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -6901,7 +7000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -6909,7 +7008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -6917,7 +7016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -6925,7 +7024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -6933,7 +7032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -6941,7 +7040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -6949,7 +7048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -6957,7 +7056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -6965,7 +7064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -6973,7 +7072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -6981,7 +7080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -6989,7 +7088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -6997,7 +7096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -7005,7 +7104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -7013,26 +7112,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>54</v>
       </c>
       <c r="B32">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>55</v>
       </c>
       <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -7040,7 +7139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -7048,7 +7147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -7056,7 +7155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -7064,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -7072,7 +7171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -7080,7 +7179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -7088,7 +7187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>63</v>
       </c>
@@ -7096,7 +7195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>64</v>
       </c>
@@ -7104,7 +7203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>65</v>
       </c>
@@ -7112,7 +7211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -7120,7 +7219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>67</v>
       </c>
@@ -7128,7 +7227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>68</v>
       </c>
@@ -7136,7 +7235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>69</v>
       </c>
@@ -7144,7 +7243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -7301,6 +7400,14 @@
         <v>89</v>
       </c>
       <c r="B67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
         <v>0</v>
       </c>
     </row>
@@ -7311,7 +7418,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -7854,6 +7961,14 @@
         <v>0</v>
       </c>
     </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
